--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N85_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N85_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.44158957202774</v>
+        <v>10.14675830545451</v>
       </c>
       <c r="D2" t="n">
-        <v>11.73051661540242</v>
+        <v>1.906208950002894</v>
       </c>
       <c r="E2" t="n">
-        <v>16.42390483730169</v>
+        <v>2.668884536061525</v>
       </c>
       <c r="F2" t="n">
-        <v>6.704141234298878</v>
+        <v>1.089422950573568</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.40496359004975</v>
+        <v>4.290806583383084</v>
       </c>
       <c r="D3" t="n">
-        <v>27.4717242543144</v>
+        <v>4.464155191326089</v>
       </c>
       <c r="E3" t="n">
-        <v>16.42390483730169</v>
+        <v>2.668884536061525</v>
       </c>
       <c r="F3" t="n">
-        <v>6.704141234298878</v>
+        <v>1.089422950573568</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.85397078632787</v>
+        <v>3.38877025277828</v>
       </c>
       <c r="D4" t="n">
-        <v>19.5555092464222</v>
+        <v>3.177770252543608</v>
       </c>
       <c r="E4" t="n">
-        <v>16.42390483730169</v>
+        <v>2.668884536061525</v>
       </c>
       <c r="F4" t="n">
-        <v>6.704141234298878</v>
+        <v>1.089422950573568</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.67355216781255</v>
+        <v>4.496952227269539</v>
       </c>
       <c r="D5" t="n">
-        <v>10.95358655478146</v>
+        <v>1.779957815151987</v>
       </c>
       <c r="E5" t="n">
-        <v>16.42390483730169</v>
+        <v>2.668884536061525</v>
       </c>
       <c r="F5" t="n">
-        <v>6.704141234298878</v>
+        <v>1.089422950573568</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
